--- a/vse-loti/341410445/spec-341410445.xlsx
+++ b/vse-loti/341410445/spec-341410445.xlsx
@@ -83,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -95,6 +95,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -463,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -749,18 +752,25 @@
         <v>1441492.79</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>НДС 22 %, ставка из документа: "НДС 22%" — Formirovanie NMTsD.txt; суммы источника указаны с НДС: "с учетом НДС 22%." — Формирование НМЦД.docx. «с НДС» — сумма из документа, «без НДС» = сумма ÷ 1,22.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>Источник: Формирование НМЦД.docx</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14"/>
+    <row r="15"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A12:B14"/>
+    <mergeCell ref="A13:B15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vse-loti/341410445/spec-341410445.xlsx
+++ b/vse-loti/341410445/spec-341410445.xlsx
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -478,6 +478,7 @@
     <col width="20.28515625" customWidth="1" min="7" max="7"/>
     <col width="18.85546875" customWidth="1" min="8" max="8"/>
     <col width="16.42578125" customWidth="1" min="9" max="9"/>
+    <col width="18.85546875" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -513,17 +514,22 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Цена за т (без НДС)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Стоимость (без НДС)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Цена за т (без НДС)</t>
-        </is>
-      </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Цена за т (с НДС)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Стоимость (с НДС)</t>
         </is>
       </c>
     </row>
@@ -553,13 +559,16 @@
         <v>4.418</v>
       </c>
       <c r="G2" s="5" t="n">
+        <v>97932.94</v>
+      </c>
+      <c r="H2" s="5" t="n">
         <v>432659.8</v>
-      </c>
-      <c r="H2" s="5" t="n">
-        <v>97932.94</v>
       </c>
       <c r="I2" s="5" t="n">
         <v>119478.18</v>
+      </c>
+      <c r="J2" s="5" t="n">
+        <v>527844.96</v>
       </c>
     </row>
     <row r="3">
@@ -588,13 +597,16 @@
         <v>3.708</v>
       </c>
       <c r="G3" s="5" t="n">
+        <v>79423.24000000001</v>
+      </c>
+      <c r="H3" s="5" t="n">
         <v>294472.92</v>
-      </c>
-      <c r="H3" s="5" t="n">
-        <v>79423.24000000001</v>
       </c>
       <c r="I3" s="5" t="n">
         <v>96896.36</v>
+      </c>
+      <c r="J3" s="5" t="n">
+        <v>359256.96</v>
       </c>
     </row>
     <row r="4">
@@ -623,13 +635,16 @@
         <v>2.969</v>
       </c>
       <c r="G4" s="5" t="n">
+        <v>80779.67999999999</v>
+      </c>
+      <c r="H4" s="5" t="n">
         <v>239828.46</v>
-      </c>
-      <c r="H4" s="5" t="n">
-        <v>80779.67999999999</v>
       </c>
       <c r="I4" s="5" t="n">
         <v>98551.21000000001</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>292590.72</v>
       </c>
     </row>
     <row r="5">
@@ -655,11 +670,14 @@
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
-      <c r="G5" s="5" t="n">
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" s="5" t="n">
         <v>50832.12</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" s="5" t="n">
+        <v>62015.19</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -684,11 +702,14 @@
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
-      <c r="G6" s="5" t="n">
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" s="5" t="n">
         <v>84604.03</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" s="5" t="n">
+        <v>103216.92</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -713,11 +734,14 @@
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
-      <c r="G7" s="5" t="n">
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" s="5" t="n">
         <v>79154.13</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" s="5" t="n">
+        <v>96568.03999999999</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -729,7 +753,16 @@
         <v>11.095</v>
       </c>
       <c r="G8" s="8" t="n">
+        <v>106494.05</v>
+      </c>
+      <c r="H8" s="8" t="n">
         <v>1181551.46</v>
+      </c>
+      <c r="I8" s="8" t="n">
+        <v>129922.74</v>
+      </c>
+      <c r="J8" s="8" t="n">
+        <v>1441492.78</v>
       </c>
     </row>
     <row r="9">
@@ -738,7 +771,7 @@
           <t>НМЦК из обоснования:</t>
         </is>
       </c>
-      <c r="G9" s="8" t="n">
+      <c r="H9" s="8" t="n">
         <v>1181551.47</v>
       </c>
     </row>
@@ -748,7 +781,7 @@
           <t>НМЦК с НДС 22%:</t>
         </is>
       </c>
-      <c r="F10" s="8" t="n">
+      <c r="J10" s="8" t="n">
         <v>1441492.79</v>
       </c>
     </row>

--- a/vse-loti/341410445/spec-341410445.xlsx
+++ b/vse-loti/341410445/spec-341410445.xlsx
@@ -83,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -95,6 +95,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
@@ -466,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -648,83 +651,47 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Отвод крутоизогнутый Ø426×8 мм</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>426×8</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" s="5" t="n">
-        <v>50832.12</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" s="5" t="n">
-        <v>62015.19</v>
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Прочие позиции лота (3) — не трубы, в трубную часть и в цену за тонну не входят</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Отвод крутоизогнутый Ø530×8 мм</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>530×8</t>
-        </is>
-      </c>
+          <t>Отвод крутоизогнутый Ø426×8 мм</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr"/>
       <c r="D6" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" s="5" t="n">
-        <v>84604.03</v>
-      </c>
-      <c r="I6" t="inlineStr"/>
+        <v>50832.12</v>
+      </c>
       <c r="J6" s="5" t="n">
-        <v>103216.92</v>
+        <v>62015.19</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Отвод крутоизогнутый Ø630×8 мм</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>630×8</t>
-        </is>
-      </c>
+          <t>Отвод крутоизогнутый Ø530×8 мм</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr"/>
       <c r="D7" s="3" t="n">
         <v>2</v>
       </c>
@@ -733,77 +700,120 @@
           <t>шт</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" s="5" t="n">
+        <v>84604.03</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>103216.92</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Отвод крутоизогнутый Ø630×8 мм</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr"/>
+      <c r="D8" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="n">
         <v>79154.13</v>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" s="5" t="n">
+      <c r="J8" s="5" t="n">
         <v>96568.03999999999</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>ИТОГО</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="n">
-        <v>11.095</v>
-      </c>
-      <c r="G8" s="8" t="n">
-        <v>106494.05</v>
-      </c>
-      <c r="H8" s="8" t="n">
-        <v>1181551.46</v>
-      </c>
-      <c r="I8" s="8" t="n">
-        <v>129922.74</v>
-      </c>
-      <c r="J8" s="8" t="n">
-        <v>1441492.78</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>НМЦК из обоснования:</t>
-        </is>
+          <t>ИТОГО трубная часть</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="n">
+        <v>11.095</v>
+      </c>
+      <c r="G9" s="8" t="n">
+        <v>87152.88</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>1181551.47</v>
+        <v>966961.1800000001</v>
+      </c>
+      <c r="I9" s="8" t="n">
+        <v>106326.51</v>
+      </c>
+      <c r="J9" s="8" t="n">
+        <v>1179692.64</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
+          <t>ВСЕГО по лоту (трубы + прочее)</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="n">
+        <v>1181551.46</v>
+      </c>
+      <c r="J10" s="8" t="n">
+        <v>1441492.78</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>НМЦК из обоснования:</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="n">
+        <v>1181551.47</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
           <t>НМЦК с НДС 22%:</t>
         </is>
       </c>
-      <c r="J10" s="8" t="n">
+      <c r="J12" s="8" t="n">
         <v>1441492.79</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="9" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>Трубная часть лота: 3 из 6 позиций; остальное — не трубы (отвод, …) — показано ниже отдельным блоком, без массы и цены за тонну. «ИТОГО трубная часть» — только трубы, «ВСЕГО по лоту» — все позиции. Доля трубной части в НМЦК: 81.84 %.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>НДС 22 %, ставка из документа: "НДС 22%" — Formirovanie NMTsD.txt; суммы источника указаны с НДС: "с учетом НДС 22%." — Формирование НМЦД.docx. «с НДС» — сумма из документа, «без НДС» = сумма ÷ 1,22.</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="10" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t>Источник: Формирование НМЦД.docx</t>
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15"/>
+    <row r="17"/>
+    <row r="18"/>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A13:B15"/>
+  <mergeCells count="2">
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A16:B18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
